--- a/public/data/pedido quimicos campaña 2026 valorizado.xlsx
+++ b/public/data/pedido quimicos campaña 2026 valorizado.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://fincalaseis-my.sharepoint.com/personal/compras_fincalaseis_com_ar/Documents/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2122" documentId="8_{2CB4EE34-6C5C-4BFC-A733-82F62E15FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00376574-496D-4567-ABF5-B1CA161FF298}"/>
+  <xr:revisionPtr revIDLastSave="2128" documentId="8_{2CB4EE34-6C5C-4BFC-A733-82F62E15FD2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{EA27411A-0DBB-4F44-8860-72249C31148D}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{8EF26D9B-9BDD-40EA-9926-EAD75B18C35F}"/>
+    <workbookView xWindow="-25320" yWindow="-120" windowWidth="25440" windowHeight="15270" xr2:uid="{8EF26D9B-9BDD-40EA-9926-EAD75B18C35F}"/>
   </bookViews>
   <sheets>
     <sheet name="Datos" sheetId="1" r:id="rId1"/>
@@ -1287,22 +1287,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>556411</xdr:colOff>
+      <xdr:colOff>575272</xdr:colOff>
       <xdr:row>1</xdr:row>
-      <xdr:rowOff>9431</xdr:rowOff>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>1009084</xdr:colOff>
-      <xdr:row>7</xdr:row>
-      <xdr:rowOff>182754</xdr:rowOff>
+      <xdr:colOff>1070383</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>13804</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Imagen 1">
+        <xdr:cNvPr id="3" name="Imagen 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28ECBAF6-A735-4495-9483-4BE301D39F6B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9A017CD1-7551-4D00-BB51-D4282A4C3861}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -1318,8 +1318,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="6535470" y="198045"/>
-          <a:ext cx="2055891" cy="1163546"/>
+          <a:off x="6554331" y="188614"/>
+          <a:ext cx="2098329" cy="1192640"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -10309,7 +10309,7 @@
         <v>164</v>
       </c>
       <c r="H1" s="8">
-        <v>1505</v>
+        <v>1520</v>
       </c>
       <c r="I1" s="2"/>
     </row>
@@ -10334,11 +10334,11 @@
       </c>
       <c r="K3" s="27">
         <f>SUM(L3:M3)</f>
-        <v>315207.52823920269</v>
+        <v>314252.21052631584</v>
       </c>
       <c r="L3" s="28">
         <f>SUMIFS(L:L, H:H, "INSUMOS DE CAMPAÑA", O:O, "Cumplido")</f>
-        <v>315003.52823920269</v>
+        <v>314048.21052631584</v>
       </c>
       <c r="M3" s="29">
         <f>SUMIFS(L:L, H:H, "INSUMOS DE CAMPAÑA", O:O, "Pendiente")</f>
@@ -10373,11 +10373,11 @@
       </c>
       <c r="K6" s="34">
         <f>SUM(K3:K5)</f>
-        <v>434430.56003920268</v>
+        <v>433475.24232631584</v>
       </c>
       <c r="L6" s="34">
         <f>SUM(L3:L5)</f>
-        <v>367660.04003920266</v>
+        <v>366704.72232631582</v>
       </c>
       <c r="M6" s="35">
         <f>SUM(M3:M5)</f>
@@ -10390,15 +10390,15 @@
       </c>
       <c r="K7" s="36">
         <f>K6*H1</f>
-        <v>653817992.85900009</v>
+        <v>658882368.33600008</v>
       </c>
       <c r="L7" s="36">
         <f>L6*H1</f>
-        <v>553328360.25900006</v>
+        <v>557391177.93600011</v>
       </c>
       <c r="M7" s="37">
         <f>M6*H1</f>
-        <v>100489632.60000001</v>
+        <v>101491190.40000001</v>
       </c>
     </row>
     <row r="9" spans="1:19" s="3" customFormat="1" x14ac:dyDescent="0.25">
@@ -12251,11 +12251,11 @@
       </c>
       <c r="K41" s="2">
         <f t="shared" si="0"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L41" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2417.9601328903655</v>
+        <v>2394.0986842105262</v>
       </c>
       <c r="M41" s="1">
         <v>46037</v>
@@ -12309,11 +12309,11 @@
       </c>
       <c r="K42" s="2">
         <f t="shared" ref="K42:K73" si="1">IF(I42="$", J42/$H$1, IF(I42="U$D", J42*1, 0))</f>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L42" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2417.9601328903655</v>
+        <v>2394.0986842105262</v>
       </c>
       <c r="M42" s="1">
         <v>46037</v>
@@ -12367,11 +12367,11 @@
       </c>
       <c r="K43" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L43" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2468.2923588039871</v>
+        <v>2443.9342105263158</v>
       </c>
       <c r="M43" s="1">
         <v>46063</v>
@@ -12425,11 +12425,11 @@
       </c>
       <c r="K44" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L44" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2468.2923588039871</v>
+        <v>2443.9342105263158</v>
       </c>
       <c r="M44" s="1">
         <v>46066</v>
@@ -12483,11 +12483,11 @@
       </c>
       <c r="K45" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L45" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1781.0897009966777</v>
+        <v>1763.5131578947367</v>
       </c>
       <c r="M45" s="1">
         <v>46070</v>
@@ -12541,11 +12541,11 @@
       </c>
       <c r="K46" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L46" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2228.039867109635</v>
+        <v>2206.0526315789475</v>
       </c>
       <c r="M46" s="1">
         <v>46073</v>
@@ -12599,11 +12599,11 @@
       </c>
       <c r="K47" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L47" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2295.1495016611298</v>
+        <v>2272.5</v>
       </c>
       <c r="M47" s="1">
         <v>46077</v>
@@ -12657,11 +12657,11 @@
       </c>
       <c r="K48" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L48" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2407.8936877076417</v>
+        <v>2384.1315789473683</v>
       </c>
       <c r="M48" s="1">
         <v>46080</v>
@@ -12715,11 +12715,11 @@
       </c>
       <c r="K49" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L49" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2301.8604651162791</v>
+        <v>2279.144736842105</v>
       </c>
       <c r="M49" s="1">
         <v>46085</v>
@@ -12773,11 +12773,11 @@
       </c>
       <c r="K50" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L50" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2637.4086378737543</v>
+        <v>2611.3815789473683</v>
       </c>
       <c r="M50" s="1">
         <v>46087</v>
@@ -12831,11 +12831,11 @@
       </c>
       <c r="K51" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L51" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1876.3853820598008</v>
+        <v>1857.8684210526317</v>
       </c>
       <c r="M51" s="1">
         <v>46094</v>
@@ -12889,11 +12889,11 @@
       </c>
       <c r="K52" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L52" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2052.2126245847176</v>
+        <v>2031.9605263157894</v>
       </c>
       <c r="M52" s="1">
         <v>46095</v>
@@ -12947,11 +12947,11 @@
       </c>
       <c r="K53" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L53" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2122.0066445182724</v>
+        <v>2101.0657894736842</v>
       </c>
       <c r="M53" s="1">
         <v>46098</v>
@@ -13008,11 +13008,11 @@
       </c>
       <c r="K54" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L54" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1879.0697674418607</v>
+        <v>1860.5263157894738</v>
       </c>
       <c r="M54" s="1">
         <v>46103</v>
@@ -13069,11 +13069,11 @@
       </c>
       <c r="K55" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L55" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2547.4817275747509</v>
+        <v>2522.3421052631579</v>
       </c>
       <c r="M55" s="1">
         <v>46106</v>
@@ -13130,11 +13130,11 @@
       </c>
       <c r="K56" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L56" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2024.0265780730899</v>
+        <v>2004.0526315789473</v>
       </c>
       <c r="M56" s="1">
         <v>46108</v>
@@ -13191,11 +13191,11 @@
       </c>
       <c r="K57" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L57" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2116.6378737541527</v>
+        <v>2095.75</v>
       </c>
       <c r="M57" s="1">
         <v>46107</v>
@@ -13252,11 +13252,11 @@
       </c>
       <c r="K58" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L58" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2378.3654485049833</v>
+        <v>2354.894736842105</v>
       </c>
       <c r="M58" s="1">
         <v>46111</v>
@@ -13313,11 +13313,11 @@
       </c>
       <c r="K59" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L59" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2288.4385382059804</v>
+        <v>2265.8552631578946</v>
       </c>
       <c r="M59" s="1">
         <v>46112</v>
@@ -13374,11 +13374,11 @@
       </c>
       <c r="K60" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L60" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2440.1063122923588</v>
+        <v>2416.0263157894738</v>
       </c>
       <c r="M60" s="1">
         <v>46113</v>
@@ -13435,11 +13435,11 @@
       </c>
       <c r="K61" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L61" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2013.2890365448507</v>
+        <v>1993.421052631579</v>
       </c>
       <c r="M61" s="1">
         <v>46118</v>
@@ -13496,11 +13496,11 @@
       </c>
       <c r="K62" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L62" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2480.3720930232562</v>
+        <v>2455.8947368421054</v>
       </c>
       <c r="M62" s="1">
         <v>46120</v>
@@ -13557,11 +13557,11 @@
       </c>
       <c r="K63" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L63" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2175.6943521594685</v>
+        <v>2154.2236842105262</v>
       </c>
       <c r="M63" s="1">
         <v>46121</v>
@@ -13618,11 +13618,11 @@
       </c>
       <c r="K64" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L64" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2266.9634551495019</v>
+        <v>2244.5921052631579</v>
       </c>
       <c r="M64" s="1">
         <v>46125</v>
@@ -13679,11 +13679,11 @@
       </c>
       <c r="K65" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L65" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2026.7109634551496</v>
+        <v>2006.7105263157894</v>
       </c>
       <c r="M65" s="1">
         <v>46127</v>
@@ -13740,11 +13740,11 @@
       </c>
       <c r="K66" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L66" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2168.9833887043192</v>
+        <v>2147.5789473684208</v>
       </c>
       <c r="M66" s="1">
         <v>46129</v>
@@ -13801,11 +13801,11 @@
       </c>
       <c r="K67" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L67" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2151.5348837209303</v>
+        <v>2130.3026315789475</v>
       </c>
       <c r="M67" s="1">
         <v>46143</v>
@@ -13862,11 +13862,11 @@
       </c>
       <c r="K68" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L68" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2007.9202657807311</v>
+        <v>1988.1052631578948</v>
       </c>
       <c r="M68" s="1">
         <v>46147</v>
@@ -13923,11 +13923,11 @@
       </c>
       <c r="K69" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L69" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1888.4651162790699</v>
+        <v>1869.828947368421</v>
       </c>
       <c r="M69" s="1">
         <v>46134</v>
@@ -13984,11 +13984,11 @@
       </c>
       <c r="K70" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L70" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1932.7574750830565</v>
+        <v>1913.6842105263158</v>
       </c>
       <c r="M70" s="1">
         <v>46136</v>
@@ -14045,11 +14045,11 @@
       </c>
       <c r="K71" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L71" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1970.3388704318938</v>
+        <v>1950.8947368421052</v>
       </c>
       <c r="M71" s="1">
         <v>46157</v>
@@ -14106,11 +14106,11 @@
       </c>
       <c r="K72" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L72" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1990.4717607973423</v>
+        <v>1970.828947368421</v>
       </c>
       <c r="M72" s="1">
         <v>46161</v>
@@ -14167,11 +14167,11 @@
       </c>
       <c r="K73" s="2">
         <f t="shared" si="1"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L73" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2100.5315614617944</v>
+        <v>2079.8026315789475</v>
       </c>
       <c r="M73" s="1">
         <v>46164</v>
@@ -14228,11 +14228,11 @@
       </c>
       <c r="K74" s="2">
         <f t="shared" ref="K74:K105" si="2">IF(I74="$", J74/$H$1, IF(I74="U$D", J74*1, 0))</f>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L74" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1904.5714285714287</v>
+        <v>1885.7763157894735</v>
       </c>
       <c r="M74" s="1">
         <v>46150</v>
@@ -14283,11 +14283,11 @@
       </c>
       <c r="K75" s="2">
         <f t="shared" si="2"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L75" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2155.56146179402</v>
+        <v>2134.2894736842104</v>
       </c>
       <c r="M75" s="1">
         <v>46162</v>
@@ -14338,11 +14338,11 @@
       </c>
       <c r="K76" s="2">
         <f t="shared" si="2"/>
-        <v>67.10963455149502</v>
+        <v>66.44736842105263</v>
       </c>
       <c r="L76" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1989.1295681063125</v>
+        <v>1969.5</v>
       </c>
       <c r="M76" s="1">
         <v>46185</v>
@@ -14393,11 +14393,11 @@
       </c>
       <c r="K77" s="2">
         <f t="shared" si="2"/>
-        <v>91.362126245847179</v>
+        <v>90.46052631578948</v>
       </c>
       <c r="L77" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2631.2292358803988</v>
+        <v>2605.2631578947371</v>
       </c>
       <c r="M77" s="1">
         <v>46069</v>
@@ -14451,11 +14451,11 @@
       </c>
       <c r="K78" s="2">
         <f t="shared" si="2"/>
-        <v>91.362126245847179</v>
+        <v>90.46052631578948</v>
       </c>
       <c r="L78" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2583.7209302325582</v>
+        <v>2558.2236842105267</v>
       </c>
       <c r="M78" s="1">
         <v>46081</v>
@@ -14509,11 +14509,11 @@
       </c>
       <c r="K79" s="2">
         <f t="shared" si="2"/>
-        <v>91.362126245847179</v>
+        <v>90.46052631578948</v>
       </c>
       <c r="L79" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2631.2292358803988</v>
+        <v>2605.2631578947371</v>
       </c>
       <c r="M79" s="1">
         <v>46088</v>
@@ -14567,11 +14567,11 @@
       </c>
       <c r="K80" s="2">
         <f t="shared" si="2"/>
-        <v>91.362126245847179</v>
+        <v>90.46052631578948</v>
       </c>
       <c r="L80" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2631.2292358803988</v>
+        <v>2605.2631578947371</v>
       </c>
       <c r="M80" s="1">
         <v>46101</v>
@@ -14628,11 +14628,11 @@
       </c>
       <c r="K81" s="2">
         <f t="shared" si="2"/>
-        <v>91.362126245847179</v>
+        <v>90.46052631578948</v>
       </c>
       <c r="L81" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2558.1395348837209</v>
+        <v>2532.8947368421054</v>
       </c>
       <c r="M81" s="1">
         <v>46114</v>
@@ -14686,11 +14686,11 @@
       </c>
       <c r="K82" s="2">
         <f t="shared" si="2"/>
-        <v>91.362126245847179</v>
+        <v>90.46052631578948</v>
       </c>
       <c r="L82" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>2521.5946843853822</v>
+        <v>2496.7105263157896</v>
       </c>
       <c r="M82" s="1">
         <v>46129</v>
@@ -14747,11 +14747,11 @@
       </c>
       <c r="K83" s="2">
         <f t="shared" si="2"/>
-        <v>91.362126245847179</v>
+        <v>90.46052631578948</v>
       </c>
       <c r="L83" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1352.1594684385384</v>
+        <v>1338.8157894736844</v>
       </c>
       <c r="M83" s="1">
         <v>46153</v>
@@ -14802,11 +14802,11 @@
       </c>
       <c r="K84" s="2">
         <f t="shared" si="2"/>
-        <v>102.99003322259136</v>
+        <v>101.97368421052632</v>
       </c>
       <c r="L84" s="2">
         <f>Tabla1[[#This Row],[Importe]]*Tabla1[[#This Row],[Cantidad]]</f>
-        <v>1524.2524916943523</v>
+        <v>1509.2105263157896</v>
       </c>
       <c r="M84" s="1">
         <v>46153</v>
@@ -16047,7 +16047,7 @@
         <v>3.15</v>
       </c>
       <c r="K106" s="2">
-        <f t="shared" ref="K106:K137" si="3">IF(I106="$", J106/$H$1, IF(I106="U$D", J106*1, 0))</f>
+        <f t="shared" ref="K106:K119" si="3">IF(I106="$", J106/$H$1, IF(I106="U$D", J106*1, 0))</f>
         <v>3.15</v>
       </c>
       <c r="L106" s="2">
